--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260602.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260602.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>1,101,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>群光電子</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,681,000</t>
+          <t>953,704,462</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>群光電子</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>953,704,462</t>
+          <t>6,681,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
